--- a/bigdata2/작업형1 연습(랜덤숫자 추출기).xlsx
+++ b/bigdata2/작업형1 연습(랜덤숫자 추출기).xlsx
@@ -1,30 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DW-203\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KHK\PythonBasic\bigdata2\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB379456-F94B-4F90-8C48-362E01AD6DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
+  <si>
+    <t>난관</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금 아쉬운</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -350,48 +375,60 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1">
         <f ca="1">RANDBETWEEN(1,39)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="1">
         <v>46181</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/bigdata2/작업형1 연습(랜덤숫자 추출기).xlsx
+++ b/bigdata2/작업형1 연습(랜덤숫자 추출기).xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KHK\PythonBasic\bigdata2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB379456-F94B-4F90-8C48-362E01AD6DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,20 +35,92 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>난관</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>조금 아쉬운</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>굿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>굿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보류남발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.9 오전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어려버!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>easy!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매우 중요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>굿!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당일 오전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당일 오후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.9 오후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발문 오해석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여전히 고전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본기 너무 중요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여전히 고전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(오후에 추가!)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iloc 기본기…</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -375,60 +446,156 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1">
         <f ca="1">RANDBETWEEN(1,39)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="1">
         <v>46181</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>46182</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/bigdata2/작업형1 연습(랜덤숫자 추출기).xlsx
+++ b/bigdata2/작업형1 연습(랜덤숫자 추출기).xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KHK\PythonBasic\bigdata2\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056E2E7E-CFF2-45A9-8FC4-C9B0E36C4CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>난관</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -114,13 +115,25 @@
   </si>
   <si>
     <t>iloc 기본기…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당일 저녁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.9 저녁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발문 또 오해석!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -446,8 +459,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
@@ -457,13 +470,13 @@
     <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1">
         <f ca="1">RANDBETWEEN(1,39)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B2" s="1">
         <v>46181</v>
       </c>
@@ -476,8 +489,11 @@
       <c r="E2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>35</v>
       </c>
@@ -485,7 +501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>23</v>
       </c>
@@ -498,8 +514,11 @@
       <c r="E4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>4</v>
       </c>
@@ -512,8 +531,11 @@
       <c r="E5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>22</v>
       </c>
@@ -527,7 +549,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>16</v>
       </c>
@@ -538,7 +560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>46182</v>
       </c>
@@ -548,8 +570,11 @@
       <c r="D9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>36</v>
       </c>
@@ -560,7 +585,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>6</v>
       </c>
@@ -568,7 +593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>2</v>
       </c>
@@ -579,7 +604,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>7</v>
       </c>
@@ -587,7 +612,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>19</v>
       </c>

--- a/bigdata2/작업형1 연습(랜덤숫자 추출기).xlsx
+++ b/bigdata2/작업형1 연습(랜덤숫자 추출기).xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KHK\PythonBasic\bigdata2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056E2E7E-CFF2-45A9-8FC4-C9B0E36C4CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="-120" windowWidth="13860" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
   <si>
     <t>난관</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -118,22 +118,86 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>당일 저녁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>6.9 저녁</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>발문 또 오해석!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.10 오전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.10 오전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여전히 고전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가까스로 통과!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통과(2% 부족)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통과!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금 고전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여전히 고전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당일 오전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평일/주말 구분에서 바로 녹다운 ㅎ….</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>isnull()? isnan?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당일 오후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.10 오후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통과!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통과!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아깝게 틀림!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여전히 고전</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -459,24 +523,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1">
         <f ca="1">RANDBETWEEN(1,39)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1">
         <v>46181</v>
       </c>
@@ -490,10 +556,16 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>35</v>
       </c>
@@ -501,7 +573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>23</v>
       </c>
@@ -515,10 +587,13 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>4</v>
       </c>
@@ -534,8 +609,14 @@
       <c r="F5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>22</v>
       </c>
@@ -548,8 +629,14 @@
       <c r="E6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>16</v>
       </c>
@@ -560,7 +647,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>46182</v>
       </c>
@@ -571,10 +658,13 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>36</v>
       </c>
@@ -584,8 +674,14 @@
       <c r="D10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>6</v>
       </c>
@@ -593,7 +689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>2</v>
       </c>
@@ -603,8 +699,11 @@
       <c r="D12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>7</v>
       </c>
@@ -612,7 +711,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>19</v>
       </c>
@@ -621,6 +720,39 @@
       </c>
       <c r="D14" t="s">
         <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="1">
+        <v>46183</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -628,4 +760,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/bigdata2/작업형1 연습(랜덤숫자 추출기).xlsx
+++ b/bigdata2/작업형1 연습(랜덤숫자 추출기).xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t>난관</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -170,10 +170,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>당일 오후</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>6.10 오후</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -191,6 +187,34 @@
   </si>
   <si>
     <t>여전히 고전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맞추긴 했으나, 조금 정교한 풀이를… ㅋㅋ!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reset_index…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>.index….</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>함수에서 난항!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오픈북 ㅋㅋ;;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맞췄으나 함수가?? 괜차늠!! 굿!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오픈북 ㅋㅋㅋ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -524,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
@@ -536,13 +560,13 @@
     <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1">
         <f ca="1">RANDBETWEEN(1,39)</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="1">
         <v>46181</v>
       </c>
@@ -562,10 +586,13 @@
         <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="I2">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>35</v>
       </c>
@@ -573,7 +600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>23</v>
       </c>
@@ -593,7 +620,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>4</v>
       </c>
@@ -613,10 +640,10 @@
         <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>22</v>
       </c>
@@ -633,10 +660,10 @@
         <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>16</v>
       </c>
@@ -647,7 +674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>46182</v>
       </c>
@@ -661,10 +688,13 @@
         <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="G9">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>36</v>
       </c>
@@ -678,10 +708,13 @@
         <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>6</v>
       </c>
@@ -689,7 +722,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>2</v>
       </c>
@@ -702,8 +735,11 @@
       <c r="E12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>7</v>
       </c>
@@ -711,7 +747,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>19</v>
       </c>
@@ -725,34 +761,69 @@
         <v>28</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="G14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>46183</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
       </c>
-      <c r="D16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="D16">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>30</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>13</v>
       </c>
       <c r="C18" t="s">
         <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="1">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/bigdata2/작업형1 연습(랜덤숫자 추출기).xlsx
+++ b/bigdata2/작업형1 연습(랜덤숫자 추출기).xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KHK\PythonBasic\bigdata2\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBBF5EE-84E0-4215-A8EC-E7889DCA63FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-120" windowWidth="13860" windowHeight="15720"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
   <si>
     <t>난관</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -221,7 +222,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -547,7 +548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -563,7 +564,7 @@
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1">
         <f ca="1">RANDBETWEEN(1,39)</f>
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -619,6 +620,9 @@
       <c r="G4" t="s">
         <v>27</v>
       </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5">
@@ -824,6 +828,9 @@
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -834,7 +841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
